--- a/AAII_Financials/Yearly/VLMTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VLMTY_YR_FIN.xlsx
@@ -302,7 +302,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -344,7 +344,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -653,135 +653,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5548200</v>
+      </c>
+      <c r="E8" s="3">
         <v>6114700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5422700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4475200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4574900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3980500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3807000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3672000</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3982800</v>
+      </c>
+      <c r="E9" s="3">
         <v>4535200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4071800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3345800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3469100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3001900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2931100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2825400</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1565400</v>
+      </c>
+      <c r="E10" s="3">
         <v>1579500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1350900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1129300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1105800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>978600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>875900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>846500</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -793,35 +805,39 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>127300</v>
+      </c>
+      <c r="E12" s="3">
         <v>126000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>101500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>93300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>91700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>79700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>75600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>76800</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -846,63 +862,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E14" s="3">
         <v>19900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-10700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>15900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>21800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>26400</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>156300</v>
+      </c>
+      <c r="E15" s="3">
         <v>151400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>163500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>95500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>88100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>81900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>77900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>91300</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -911,62 +936,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>5016000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5551000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4967400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4013400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4167600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3665100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3542500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3442600</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>532100</v>
+      </c>
+      <c r="E18" s="3">
         <v>563700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>455300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>461700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>407300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>315300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>264500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>229300</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -978,143 +1010,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>10200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>8600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2400</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>677100</v>
+      </c>
+      <c r="E21" s="3">
         <v>720700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>614500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>547000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>486900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>391700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>337800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>318200</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E22" s="3">
         <v>42000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1100</v>
-      </c>
-      <c r="G22" s="3">
-        <v>13500</v>
       </c>
       <c r="H22" s="3">
         <v>13500</v>
       </c>
       <c r="I22" s="3">
+        <v>13500</v>
+      </c>
+      <c r="J22" s="3">
         <v>6900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14400</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>396500</v>
+      </c>
+      <c r="E23" s="3">
         <v>522800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>460600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>450400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>374300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>301900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>233600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>189700</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>105600</v>
+      </c>
+      <c r="E24" s="3">
         <v>126000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>112600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>91700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>75200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>60700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>44400</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1139,63 +1187,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>290900</v>
+      </c>
+      <c r="E26" s="3">
         <v>396800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>360200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>337800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>282600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>226700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>172900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>145300</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>289900</v>
+      </c>
+      <c r="E27" s="3">
         <v>394600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>360200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>336600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>282600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>225600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>172900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>145300</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1220,9 +1277,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1247,9 +1307,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1274,9 +1337,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1301,63 +1367,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E32" s="3">
         <v>5500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-10200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-8600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2400</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>289900</v>
+      </c>
+      <c r="E33" s="3">
         <v>394600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>360200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>336600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>282600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>225600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>172900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>145300</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1382,68 +1457,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>289900</v>
+      </c>
+      <c r="E35" s="3">
         <v>394600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>360200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>336600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>282600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>225600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>172900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>145300</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1455,8 +1539,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1468,251 +1553,279 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>499000</v>
+      </c>
+      <c r="E41" s="3">
         <v>477500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>296000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>588000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>335200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>354600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>430500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>355400</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E42" s="3">
         <v>27600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>33100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>53500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>90500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>47100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>50400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7200</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1947600</v>
+        <v>1314800</v>
       </c>
       <c r="E43" s="3">
+        <v>1662400</v>
+      </c>
+      <c r="F43" s="3">
         <v>1696100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1253300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1213500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1181700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>957200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1021900</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>934900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1158400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>998200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>752900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>677700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>575700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>479700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>498300</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>32100</v>
+        <v>268100</v>
       </c>
       <c r="E45" s="3">
+        <v>317200</v>
+      </c>
+      <c r="F45" s="3">
         <v>62000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>39800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>59900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>20200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>17200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>26400</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>3047900</v>
+      </c>
+      <c r="E46" s="3">
         <v>3643200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3085400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2687400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2376800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2179300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1935000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1909200</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E47" s="3">
         <v>28700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>26700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>536800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>584700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>18000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>19500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>20400</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>751600</v>
+      </c>
+      <c r="E48" s="3">
         <v>771500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>641200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>532200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>539400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>481400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>398400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>425100</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>3038600</v>
+      </c>
+      <c r="E49" s="3">
         <v>3180100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2822500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1141800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1202400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1054900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>936600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>977400</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1737,9 +1850,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1764,36 +1880,42 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>84900</v>
+      </c>
+      <c r="E52" s="3">
         <v>76300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>62000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>52300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>63600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>57200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>51500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>43200</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1818,36 +1940,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>7073200</v>
+      </c>
+      <c r="E54" s="3">
         <v>7808100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6701900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5026700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4842800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3873900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3421100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3491800</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1859,8 +1987,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -1872,170 +2001,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>476200</v>
+      </c>
+      <c r="E57" s="3">
         <v>574800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>472400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>425300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>455000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>397300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>327500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>344600</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>170800</v>
+      </c>
+      <c r="E58" s="3">
         <v>161400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>203100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>277500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>48900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>78600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>44700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>21600</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>1544700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1946500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2022000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2038000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1800600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1520600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1346500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1355700</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2439200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2944600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2926200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2921600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2482000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2149000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1864000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1870800</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1427700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1478900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>660500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>263800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>563900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>224400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>186600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>242600</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E62" s="3">
         <v>59700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>49200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>33000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>73400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>39300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>40100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26400</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2060,9 +2208,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2087,9 +2238,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2114,36 +2268,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>4366900</v>
+      </c>
+      <c r="E66" s="3">
         <v>4966300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4031200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3511900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3444600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2700000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2334600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2389500</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2155,8 +2315,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2181,9 +2342,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2208,9 +2372,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2235,9 +2402,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2262,36 +2432,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>1177100</v>
+      </c>
+      <c r="E72" s="3">
         <v>1211500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1065500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>914400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>774300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>599300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>516400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>480300</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2316,9 +2492,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2343,9 +2522,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2370,36 +2552,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>2699000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2835200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2665400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1508000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1390800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1167100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1080800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1096300</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2424,68 +2612,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>289900</v>
+      </c>
+      <c r="E81" s="3">
         <v>394600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>360200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>336600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>282600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>225600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>172900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>145300</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2497,35 +2694,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>114900</v>
+      </c>
+      <c r="E83" s="3">
         <v>108300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>95100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>80700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>85600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>80800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>52700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>60000</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2550,9 +2751,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2577,9 +2781,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2604,9 +2811,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2631,9 +2841,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2658,36 +2871,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>573600</v>
+      </c>
+      <c r="E89" s="3">
         <v>389100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>38500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>548200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>650800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>331100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>325200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>349400</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2699,35 +2918,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-85900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-108300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-85500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-77300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-73400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-64000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-60700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-56400</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2752,9 +2975,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -2779,36 +3005,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-246400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-588000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>21400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-112600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-724200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-266000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-85900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-76800</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -2820,35 +3052,39 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>256800</v>
+      </c>
+      <c r="E96" s="3">
         <v>264200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>191300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>152400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>146800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>108900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>93900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>75600</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -2873,9 +3109,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -2900,9 +3139,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -2927,88 +3169,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-277500</v>
+      </c>
+      <c r="E100" s="3">
         <v>382400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-312100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-176300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>34300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-134700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-145400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-193300</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-11100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>18200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-12200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-12000</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E102" s="3">
         <v>172400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-256500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>277500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-51400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-67300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>91600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>67200</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/VLMTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VLMTY_YR_FIN.xlsx
@@ -1590,10 +1590,10 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>31100</v>
+        <v>39300</v>
       </c>
       <c r="E42" s="3">
-        <v>27600</v>
+        <v>30900</v>
       </c>
       <c r="F42" s="3">
         <v>33100</v>
@@ -1680,10 +1680,10 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>268100</v>
+        <v>259900</v>
       </c>
       <c r="E45" s="3">
-        <v>317200</v>
+        <v>313900</v>
       </c>
       <c r="F45" s="3">
         <v>62000</v>

--- a/AAII_Financials/Yearly/VLMTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VLMTY_YR_FIN.xlsx
@@ -653,147 +653,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6101900</v>
+      </c>
+      <c r="E8" s="3">
         <v>5548200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6114700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5422700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4475200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4574900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3980500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3807000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3672000</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4366600</v>
+      </c>
+      <c r="E9" s="3">
         <v>3982800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4535200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4071800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3345800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3469100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3001900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2931100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2825400</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1735400</v>
+      </c>
+      <c r="E10" s="3">
         <v>1565400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1579500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1350900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1129300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1105800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>978600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>875900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>846500</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -806,38 +818,42 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>147900</v>
+      </c>
+      <c r="E12" s="3">
         <v>127300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>126000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>101500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>93300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>91700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>79700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>75600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>76800</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,69 +881,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>54900</v>
+        <v>111500</v>
       </c>
       <c r="E14" s="3">
+        <v>62100</v>
+      </c>
+      <c r="F14" s="3">
         <v>19900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-10700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>15900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>21800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>26400</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>163200</v>
+      </c>
+      <c r="E15" s="3">
         <v>156300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>151400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>163500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>95500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>88100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>81900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>77900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>91300</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -937,68 +962,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>5016000</v>
+        <v>5473800</v>
       </c>
       <c r="E17" s="3">
+        <v>5008800</v>
+      </c>
+      <c r="F17" s="3">
         <v>5551000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4967400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4013400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4167600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3665100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3542500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3442600</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>532100</v>
+        <v>628200</v>
       </c>
       <c r="E18" s="3">
+        <v>539400</v>
+      </c>
+      <c r="F18" s="3">
         <v>563700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>455300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>461700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>407300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>315300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>264500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>229300</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1011,158 +1043,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E20" s="3">
         <v>11400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>10200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2400</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>677100</v>
+        <v>782000</v>
       </c>
       <c r="E21" s="3">
+        <v>684300</v>
+      </c>
+      <c r="F21" s="3">
         <v>720700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>614500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>547000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>486900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>391700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>337800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>318200</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E22" s="3">
         <v>92100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>42000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>10700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>13500</v>
       </c>
       <c r="I22" s="3">
         <v>13500</v>
       </c>
       <c r="J22" s="3">
+        <v>13500</v>
+      </c>
+      <c r="K22" s="3">
         <v>6900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14400</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>441500</v>
+      </c>
+      <c r="E23" s="3">
         <v>396500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>522800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>460600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>450400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>374300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>301900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>233600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>189700</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>112700</v>
+      </c>
+      <c r="E24" s="3">
         <v>105600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>126000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>112600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>91700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>75200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>60700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>44400</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1190,69 +1238,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>328800</v>
+      </c>
+      <c r="E26" s="3">
         <v>290900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>396800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>360200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>337800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>282600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>226700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>172900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>145300</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>328800</v>
+      </c>
+      <c r="E27" s="3">
         <v>289900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>394600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>360200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>336600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>282600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>225600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>172900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>145300</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1280,9 +1337,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1310,9 +1370,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1340,9 +1403,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1370,69 +1436,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-11400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-10200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-8600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2400</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>328800</v>
+      </c>
+      <c r="E33" s="3">
         <v>289900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>394600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>360200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>336600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>282600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>225600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>172900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>145300</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1460,74 +1535,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>328800</v>
+      </c>
+      <c r="E35" s="3">
         <v>289900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>394600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>360200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>336600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>282600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>225600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>172900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>145300</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1540,8 +1624,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1554,278 +1639,306 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>628200</v>
+      </c>
+      <c r="E41" s="3">
         <v>499000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>477500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>296000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>588000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>335200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>354600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>430500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>355400</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E42" s="3">
         <v>39300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>30900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>33100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>53500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>90500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>47100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>50400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7200</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1365500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1314800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1662400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1696100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1253300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1213500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1181700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>957200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1021900</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1037900</v>
+      </c>
+      <c r="E44" s="3">
         <v>934900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1158400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>998200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>752900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>677700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>575700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>479700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>498300</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>287700</v>
+      </c>
+      <c r="E45" s="3">
         <v>259900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>313900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>62000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>39800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>59900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>20200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>17200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26400</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>3348600</v>
+      </c>
+      <c r="E46" s="3">
         <v>3047900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3643200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3085400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2687400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2376800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2179300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1935000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1909200</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E47" s="3">
         <v>30000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>28700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>26700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>536800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>584700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>18000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>19500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>20400</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>868900</v>
+      </c>
+      <c r="E48" s="3">
         <v>751600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>771500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>641200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>532200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>539400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>481400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>398400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>425100</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>3334500</v>
+      </c>
+      <c r="E49" s="3">
         <v>3038600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3180100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2822500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1141800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1202400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1054900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>936600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>977400</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1853,9 +1966,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1883,39 +1999,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>69300</v>
+      </c>
+      <c r="E52" s="3">
         <v>84900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>76300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>62000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>52300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>63600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>57200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>51500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>43200</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1943,39 +2065,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>7789100</v>
+      </c>
+      <c r="E54" s="3">
         <v>7073200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7808100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6701900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5026700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4842800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3873900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3421100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3491800</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1988,8 +2116,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2002,188 +2131,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>587100</v>
+      </c>
+      <c r="E57" s="3">
         <v>476200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>574800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>472400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>425300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>455000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>397300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>327500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>344600</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>211300</v>
+      </c>
+      <c r="E58" s="3">
         <v>170800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>161400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>203100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>277500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>48900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>78600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>44700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21600</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>1544700</v>
+        <v>1487600</v>
       </c>
       <c r="E59" s="3">
+        <v>1361400</v>
+      </c>
+      <c r="F59" s="3">
         <v>1946500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2022000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2038000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1800600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1520600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1346500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1355700</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2740400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2439200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2944600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2926200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2921600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2482000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2149000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1864000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1870800</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1504100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1427700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1478900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>660500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>263800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>563900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>224400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>186600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>242600</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E62" s="3">
         <v>43500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>59700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>49200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>33000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>73400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>39300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>40100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>26400</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2211,9 +2359,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2241,9 +2392,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2271,39 +2425,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>4748200</v>
+      </c>
+      <c r="E66" s="3">
         <v>4366900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4966300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4031200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3511900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3444600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2700000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2334600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2389500</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2316,8 +2476,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2345,9 +2506,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2375,9 +2539,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2405,9 +2572,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2435,39 +2605,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>1371400</v>
+      </c>
+      <c r="E72" s="3">
         <v>1177100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1211500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1065500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>914400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>774300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>599300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>516400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>480300</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2495,9 +2671,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2525,9 +2704,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2555,39 +2737,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>3033900</v>
+      </c>
+      <c r="E76" s="3">
         <v>2699000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2835200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2665400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1508000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1390800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1167100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1080800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1096300</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2615,74 +2803,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>328800</v>
+      </c>
+      <c r="E81" s="3">
         <v>289900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>394600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>360200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>336600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>282600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>225600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>172900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>145300</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2695,38 +2892,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>132700</v>
+      </c>
+      <c r="E83" s="3">
         <v>114900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>108300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>95100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>80700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>85600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>80800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>52700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>60000</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2754,9 +2955,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2784,9 +2988,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2814,9 +3021,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2844,9 +3054,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2874,39 +3087,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>682200</v>
+      </c>
+      <c r="E89" s="3">
         <v>573600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>389100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>38500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>548200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>650800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>331100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>325200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>349400</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2919,38 +3138,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-99800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-85900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-108300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-85500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-77300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-73400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-64000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-60700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-56400</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2978,9 +3201,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3008,39 +3234,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-113900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-246400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-588000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>21400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-112600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-724200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-266000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-85900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-76800</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3053,38 +3285,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>291200</v>
+      </c>
+      <c r="E96" s="3">
         <v>256800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>264200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>191300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>152400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>146800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>108900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>93900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>75600</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3112,9 +3348,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3142,9 +3381,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3172,97 +3414,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-470800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-277500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>382400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-312100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-176300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>34300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-134700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-145400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-193300</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="E101" s="3">
         <v>3100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-11100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>18200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-12200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-12000</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E102" s="3">
         <v>52800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>172400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-256500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>277500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-51400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-67300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>91600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>67200</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
